--- a/legacy/nola_2025_results.xlsx
+++ b/legacy/nola_2025_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="1-Seed Draw" sheetId="1" state="visible" r:id="rId3"/>
@@ -105,6 +105,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="W39" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Changed to 57 from 52 based on correction to round 4 score</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -650,10 +662,10 @@
     <t xml:space="preserve">Anomalies (highlighted above)</t>
   </si>
   <si>
-    <t xml:space="preserve">Round 7 - table 4 (players 2, 16, 27, 31)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Round 7 – table 10 (players 12, 15, 21, 35)</t>
+    <t xml:space="preserve">Round 7 - table 4 (players 2, 16, 27, 31) – amended to 10-7 (for team 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round 7 – table 10 (players 12, 15, 21, 35) – amended to 10-4 (for team 2)</t>
   </si>
   <si>
     <t xml:space="preserve">Rank</t>
@@ -1073,7 +1085,7 @@
     <t xml:space="preserve">Cooper / West</t>
   </si>
   <si>
-    <t xml:space="preserve">Round 8 – table 7 (teams 2B, 8B)</t>
+    <t xml:space="preserve">Round 8 – table 7 (teams 2B, 8B) – amended to 10-6 (for team 2B)</t>
   </si>
   <si>
     <t xml:space="preserve">Final Rank</t>

--- a/legacy/nola_2025_results.xlsx
+++ b/legacy/nola_2025_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="1-Seed Draw" sheetId="1" state="visible" r:id="rId3"/>
@@ -5743,6 +5743,7 @@
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="11.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9565,7 +9566,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="24.77"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="4" style="18" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="18" width="10.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="5" width="12.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="11.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="18" width="10.75"/>
